--- a/public/templates/programacao-navios-modelo.xlsx
+++ b/public/templates/programacao-navios-modelo.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -397,19 +397,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="16.83203125"/>
+    <col min="2" max="2" customWidth="1" width="16.83203125"/>
+    <col min="3" max="3" customWidth="1" width="16.83203125"/>
+    <col min="4" max="4" customWidth="1" width="16.83203125"/>
+    <col min="5" max="5" customWidth="1" width="16.83203125"/>
+    <col min="6" max="6" customWidth="1" width="16.83203125"/>
+    <col min="7" max="7" customWidth="1" width="16.83203125"/>
+    <col min="8" max="8" customWidth="1" width="16.83203125"/>
+    <col min="9" max="9" customWidth="1" width="16.83203125"/>
+    <col min="10" max="10" customWidth="1" width="16.83203125"/>
+    <col min="11" max="11" customWidth="1" width="16.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,6 +446,9 @@
       <c r="K1" t="str">
         <v>PECÉM ETA</v>
       </c>
+      <c r="L1" t="str">
+        <v>SUAPE ETA</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -484,7 +487,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>